--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486727_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486727_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4603</v>
+        <v>7.3748</v>
       </c>
       <c r="E2" t="n">
-        <v>5.24</v>
+        <v>5.2539</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2202</v>
+        <v>2.1209</v>
       </c>
       <c r="G2" t="n">
         <v>6.6465</v>
@@ -610,13 +610,13 @@
         <v>4.2477</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3145</v>
+        <v>-0.3999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1663</v>
+        <v>-0.1524</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1482</v>
+        <v>-0.2475</v>
       </c>
       <c r="V2" t="n">
         <v>0.1628</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0709</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0478</v>
+        <v>-0.2624</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0231</v>
+        <v>1.0976</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0764</v>
@@ -688,13 +688,13 @@
         <v>0.5792</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.3241</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4136</v>
+        <v>0.1033</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5019</v>
+        <v>-0.4274</v>
       </c>
       <c r="V3" t="n">
         <v>0.6565</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.346</v>
+        <v>0.6232</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9902</v>
+        <v>-0.5144</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3363</v>
+        <v>1.1376</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9187</v>
@@ -766,13 +766,13 @@
         <v>4.0546</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1528</v>
+        <v>-0.8756</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2141</v>
+        <v>-0.7383</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0614</v>
+        <v>-0.1373</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2856</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3447</v>
+        <v>0.0897</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8198</v>
+        <v>0.5647</v>
       </c>
       <c r="F5" t="n">
         <v>-0.4751</v>
@@ -844,10 +844,10 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2207</v>
+        <v>-0.4758</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1928</v>
+        <v>-0.0622</v>
       </c>
       <c r="U5" t="n">
         <v>-0.4136</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>K. RODRIGUEZ AGUILERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0949</v>
+        <v>-0.7657</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6489</v>
+        <v>-1.2333</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5539</v>
+        <v>0.4676</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.7542</v>
+        <v>-0.334</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3723</v>
+        <v>-0.2414</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.1265</v>
+        <v>-0.0926</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7454</v>
+        <v>0.5226</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2009</v>
+        <v>0.1042</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9464</v>
+        <v>0.4184</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0088</v>
+        <v>-0.8566</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8286</v>
+        <v>-0.3456</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1802</v>
+        <v>-0.511</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.2477</v>
+        <v>-1.3515</v>
       </c>
       <c r="R6" t="n">
-        <v>4.2477</v>
+        <v>3.0892</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4303</v>
+        <v>-1.2273</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1111</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3192</v>
+        <v>-0.5374</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0896</v>
+        <v>-0.9421</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4554</v>
+        <v>0.2856</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3658</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4516</v>
+        <v>-1.1869</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7946</v>
+        <v>-0.381</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6569</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2021</v>
@@ -1000,13 +1000,13 @@
         <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.706</v>
+        <v>-0.4413</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1932</v>
+        <v>0.2205</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5128</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1228</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. RODRIGUEZ AGUILERA</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5684</v>
+        <v>-1.3886</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8125</v>
+        <v>-2.7936</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2441</v>
+        <v>1.4049</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.334</v>
+        <v>-2.7542</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2414</v>
+        <v>0.3723</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0926</v>
+        <v>-3.1265</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5226</v>
+        <v>-0.7454</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1042</v>
+        <v>1.2009</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4184</v>
+        <v>-1.9464</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8566</v>
+        <v>-2.0088</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3456</v>
+        <v>-0.8286</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.511</v>
+        <v>-1.1802</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3515</v>
+        <v>-4.2477</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0892</v>
+        <v>4.2477</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.03</v>
+        <v>-0.724</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2692</v>
+        <v>-0.2558</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7609</v>
+        <v>-0.4682</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9421</v>
+        <v>2.0896</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2856</v>
+        <v>2.4554</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2277</v>
+        <v>-0.3658</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9791</v>
+        <v>-2.5211</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0064</v>
+        <v>-2.8961</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0273</v>
+        <v>0.3749</v>
       </c>
       <c r="G9" t="n">
         <v>0.9782999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>2.7031</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1476</v>
+        <v>-0.6895</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3314</v>
+        <v>-0.2211</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8161</v>
+        <v>-0.4685</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2652</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8988</v>
+        <v>-4.7277</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5197</v>
+        <v>-3.299</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3791</v>
+        <v>-1.4287</v>
       </c>
       <c r="G10" t="n">
         <v>-5.6817</v>
@@ -1234,13 +1234,13 @@
         <v>2.3169</v>
       </c>
       <c r="S10" t="n">
-        <v>0.022</v>
+        <v>0.193</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0832</v>
+        <v>0.1375</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1051</v>
+        <v>0.0555</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5559</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.770899999999999</v>
+        <v>-1.667100000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6647</v>
+        <v>-5.561200000000001</v>
       </c>
       <c r="F11" t="n">
         <v>3.8938</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6541</v>
+        <v>-3.654100000000001</v>
       </c>
       <c r="H11" t="n">
         <v>3.7948</v>
@@ -1312,10 +1312,10 @@
         <v>23.1691</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.0683</v>
+        <v>-4.964500000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.7621</v>
+        <v>-1.6585</v>
       </c>
       <c r="U11" t="n">
         <v>-3.3062</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.3543</v>
+        <v>11.721</v>
       </c>
       <c r="E12" t="n">
-        <v>7.826</v>
+        <v>8.239599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5284</v>
+        <v>3.4813</v>
       </c>
       <c r="G12" t="n">
         <v>7.7123</v>
@@ -1390,13 +1390,13 @@
         <v>2.3169</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5575</v>
+        <v>0.9241</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6348</v>
+        <v>-0.2211</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1922</v>
+        <v>1.1452</v>
       </c>
       <c r="V12" t="n">
         <v>2.6984</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.854</v>
+        <v>2.6708</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3202</v>
+        <v>1.3894</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5338000000000001</v>
+        <v>1.2814</v>
       </c>
       <c r="G13" t="n">
         <v>0.7387</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3623</v>
+        <v>1.1791</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9027</v>
+        <v>0.9719</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5404</v>
+        <v>0.2072</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9847</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6284</v>
+        <v>1.1848</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7544999999999999</v>
+        <v>-2.4084</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1261</v>
+        <v>3.5932</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2976</v>
+        <v>-0.0582</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7581</v>
+        <v>0.0616</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0557</v>
+        <v>-0.1198</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5135</v>
+        <v>-0.2777</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4502</v>
+        <v>0.4072</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0634</v>
+        <v>-0.6849</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2159</v>
+        <v>0.2195</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2082</v>
+        <v>-0.3456</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9923</v>
+        <v>0.5651</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5446</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q14" t="n">
         <v>-4.0546</v>
       </c>
       <c r="R14" t="n">
-        <v>2.51</v>
+        <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0025</v>
+        <v>0.6757</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2957</v>
+        <v>0.0824</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7069</v>
+        <v>0.5934</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.1271</v>
+        <v>2.498</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1271</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>D. LOZANO ESCOBAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5587</v>
+        <v>0.4689</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.8221</v>
+        <v>-0.1241</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3808</v>
+        <v>0.593</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0582</v>
+        <v>0.4344</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0616</v>
+        <v>0.1586</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1198</v>
+        <v>0.2758</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2777</v>
+        <v>0.0207</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4072</v>
+        <v>0.0207</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6849</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2195</v>
+        <v>0.4137</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3456</v>
+        <v>0.1379</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5651</v>
+        <v>0.2758</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.0546</v>
+        <v>-0.1931</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1239</v>
+        <v>0.1931</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0497</v>
+        <v>0.0345</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3313</v>
+        <v>0.0482</v>
       </c>
       <c r="U15" t="n">
-        <v>0.381</v>
+        <v>-0.0137</v>
       </c>
       <c r="V15" t="n">
-        <v>2.498</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. LOZANO ESCOBAR</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.291</v>
+        <v>0.1636</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2276</v>
+        <v>0.2374</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5185</v>
+        <v>-0.0738</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4344</v>
+        <v>2.2976</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1586</v>
+        <v>-1.7581</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2758</v>
+        <v>4.0557</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0207</v>
+        <v>3.5135</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0207</v>
+        <v>0.4502</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.0634</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4137</v>
+        <v>-1.2159</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1379</v>
+        <v>-2.2082</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2758</v>
+        <v>0.9923</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1931</v>
+        <v>-4.0546</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1931</v>
+        <v>2.51</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1434</v>
+        <v>1.5377</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0552</v>
+        <v>0.7785</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0882</v>
+        <v>0.7592</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-2.1271</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0109</v>
+        <v>0.1173</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4692</v>
+        <v>0.5727</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4802</v>
+        <v>-0.4553</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2552</v>
@@ -1780,13 +1780,13 @@
         <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1765</v>
+        <v>-0.0483</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0413</v>
       </c>
       <c r="V17" t="n">
         <v>1.2277</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6611</v>
+        <v>0.1139</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.547</v>
+        <v>-2.1333</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8859</v>
+        <v>2.2473</v>
       </c>
       <c r="G18" t="n">
         <v>0.0352</v>
@@ -1858,13 +1858,13 @@
         <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5958</v>
+        <v>0.1793</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2485</v>
+        <v>0.1652</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3473</v>
+        <v>0.0141</v>
       </c>
       <c r="V18" t="n">
         <v>0.2856</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>L. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3594</v>
+        <v>-1.1389</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2522</v>
+        <v>0.3994</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1072</v>
+        <v>-1.5383</v>
       </c>
       <c r="G19" t="n">
-        <v>0.403</v>
+        <v>-0.4631</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1035</v>
+        <v>0.4412</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5064</v>
+        <v>-0.9043</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2387</v>
+        <v>1.0339</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6214</v>
+        <v>0.9932</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6172</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8357</v>
+        <v>-1.497</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7249</v>
+        <v>-0.5521</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1108</v>
+        <v>-0.945</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.8962</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5626</v>
+        <v>0.0965</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7995</v>
+        <v>0.3309</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2369</v>
+        <v>-0.2343</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. ALONSO MENOR</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6271</v>
+        <v>-1.3083</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0143</v>
+        <v>-0.5625</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6128</v>
+        <v>-0.7459</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4631</v>
+        <v>0.403</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4412</v>
+        <v>-0.1035</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9043</v>
+        <v>0.5064</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0339</v>
+        <v>2.2387</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9932</v>
+        <v>1.6214</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>0.6172</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.497</v>
+        <v>-1.8357</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5521</v>
+        <v>-1.7249</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.945</v>
+        <v>-0.1108</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7723</v>
+        <v>-2.8962</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3917</v>
+        <v>0.6137</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0828</v>
+        <v>0.4892</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3088</v>
+        <v>0.1245</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7888</v>
+        <v>-2.6137</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1961</v>
+        <v>-1.8859</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5926</v>
+        <v>-0.7279</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8934</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>0.618</v>
+        <v>0.793</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0548</v>
+        <v>0.3651</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5632</v>
+        <v>0.4279</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5133</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.4682</v>
+        <v>-7.2295</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.2044</v>
+        <v>-7.6181</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7362</v>
+        <v>0.3886</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2972</v>
@@ -2170,13 +2170,13 @@
         <v>2.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2232</v>
+        <v>1.4619</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7165</v>
+        <v>0.3028</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5066</v>
+        <v>1.159</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8842</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.7709</v>
+        <v>4.149900000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.893799999999998</v>
+        <v>-3.8938</v>
       </c>
       <c r="F23" t="n">
-        <v>6.664699999999999</v>
+        <v>8.0436</v>
       </c>
       <c r="G23" t="n">
-        <v>3.6541</v>
+        <v>3.654100000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-3.7948</v>
       </c>
       <c r="I23" t="n">
-        <v>7.449</v>
+        <v>7.448999999999998</v>
       </c>
       <c r="J23" t="n">
         <v>10.7003</v>
@@ -2239,7 +2239,7 @@
         <v>2.2715</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.723100000000001</v>
+        <v>-7.7231</v>
       </c>
       <c r="Q23" t="n">
         <v>-23.1694</v>
@@ -2248,19 +2248,19 @@
         <v>15.4463</v>
       </c>
       <c r="S23" t="n">
-        <v>6.0684</v>
+        <v>7.4472</v>
       </c>
       <c r="T23" t="n">
         <v>3.3062</v>
       </c>
       <c r="U23" t="n">
-        <v>2.762099999999999</v>
+        <v>4.1412</v>
       </c>
       <c r="V23" t="n">
         <v>0.7716000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>5.2688</v>
+        <v>5.268800000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-4.4972</v>
